--- a/output_data.xlsx
+++ b/output_data.xlsx
@@ -9,15 +9,87 @@
   <sheets>
     <sheet name="Rankings" sheetId="1" r:id="rId1"/>
     <sheet name="Accuracy" sheetId="2" r:id="rId2"/>
-    <sheet name="695" sheetId="3" r:id="rId3"/>
-    <sheet name="1787" sheetId="4" r:id="rId4"/>
+    <sheet name="188" sheetId="3" r:id="rId3"/>
+    <sheet name="238" sheetId="4" r:id="rId4"/>
+    <sheet name="401" sheetId="5" r:id="rId5"/>
+    <sheet name="494" sheetId="6" r:id="rId6"/>
+    <sheet name="503" sheetId="7" r:id="rId7"/>
+    <sheet name="540" sheetId="8" r:id="rId8"/>
+    <sheet name="573" sheetId="9" r:id="rId9"/>
+    <sheet name="581" sheetId="10" r:id="rId10"/>
+    <sheet name="761" sheetId="11" r:id="rId11"/>
+    <sheet name="910" sheetId="12" r:id="rId12"/>
+    <sheet name="1014" sheetId="13" r:id="rId13"/>
+    <sheet name="1259" sheetId="14" r:id="rId14"/>
+    <sheet name="1287" sheetId="15" r:id="rId15"/>
+    <sheet name="1296" sheetId="16" r:id="rId16"/>
+    <sheet name="1625" sheetId="17" r:id="rId17"/>
+    <sheet name="1701" sheetId="18" r:id="rId18"/>
+    <sheet name="1706" sheetId="19" r:id="rId19"/>
+    <sheet name="1710" sheetId="20" r:id="rId20"/>
+    <sheet name="1732" sheetId="21" r:id="rId21"/>
+    <sheet name="1787" sheetId="22" r:id="rId22"/>
+    <sheet name="1986" sheetId="23" r:id="rId23"/>
+    <sheet name="2056" sheetId="24" r:id="rId24"/>
+    <sheet name="2102" sheetId="25" r:id="rId25"/>
+    <sheet name="2199" sheetId="26" r:id="rId26"/>
+    <sheet name="2220" sheetId="27" r:id="rId27"/>
+    <sheet name="2383" sheetId="28" r:id="rId28"/>
+    <sheet name="2486" sheetId="29" r:id="rId29"/>
+    <sheet name="2607" sheetId="30" r:id="rId30"/>
+    <sheet name="2659" sheetId="31" r:id="rId31"/>
+    <sheet name="2834" sheetId="32" r:id="rId32"/>
+    <sheet name="3015" sheetId="33" r:id="rId33"/>
+    <sheet name="3035" sheetId="34" r:id="rId34"/>
+    <sheet name="3175" sheetId="35" r:id="rId35"/>
+    <sheet name="3297" sheetId="36" r:id="rId36"/>
+    <sheet name="3467" sheetId="37" r:id="rId37"/>
+    <sheet name="3506" sheetId="38" r:id="rId38"/>
+    <sheet name="3512" sheetId="39" r:id="rId39"/>
+    <sheet name="3539" sheetId="40" r:id="rId40"/>
+    <sheet name="3641" sheetId="41" r:id="rId41"/>
+    <sheet name="4143" sheetId="42" r:id="rId42"/>
+    <sheet name="4174" sheetId="43" r:id="rId43"/>
+    <sheet name="4191" sheetId="44" r:id="rId44"/>
+    <sheet name="4201" sheetId="45" r:id="rId45"/>
+    <sheet name="4613" sheetId="46" r:id="rId46"/>
+    <sheet name="4698" sheetId="47" r:id="rId47"/>
+    <sheet name="5000" sheetId="48" r:id="rId48"/>
+    <sheet name="5086" sheetId="49" r:id="rId49"/>
+    <sheet name="5348" sheetId="50" r:id="rId50"/>
+    <sheet name="5406" sheetId="51" r:id="rId51"/>
+    <sheet name="5454" sheetId="52" r:id="rId52"/>
+    <sheet name="6121" sheetId="53" r:id="rId53"/>
+    <sheet name="6152" sheetId="54" r:id="rId54"/>
+    <sheet name="6200" sheetId="55" r:id="rId55"/>
+    <sheet name="6328" sheetId="56" r:id="rId56"/>
+    <sheet name="6329" sheetId="57" r:id="rId57"/>
+    <sheet name="6517" sheetId="58" r:id="rId58"/>
+    <sheet name="6639" sheetId="59" r:id="rId59"/>
+    <sheet name="7287" sheetId="60" r:id="rId60"/>
+    <sheet name="7451" sheetId="61" r:id="rId61"/>
+    <sheet name="8005" sheetId="62" r:id="rId62"/>
+    <sheet name="8044" sheetId="63" r:id="rId63"/>
+    <sheet name="8214" sheetId="64" r:id="rId64"/>
+    <sheet name="8267" sheetId="65" r:id="rId65"/>
+    <sheet name="8513" sheetId="66" r:id="rId66"/>
+    <sheet name="8749" sheetId="67" r:id="rId67"/>
+    <sheet name="9449" sheetId="68" r:id="rId68"/>
+    <sheet name="9692" sheetId="69" r:id="rId69"/>
+    <sheet name="9785" sheetId="70" r:id="rId70"/>
+    <sheet name="10131" sheetId="71" r:id="rId71"/>
+    <sheet name="10907" sheetId="72" r:id="rId72"/>
+    <sheet name="11024" sheetId="73" r:id="rId73"/>
+    <sheet name="11118" sheetId="74" r:id="rId74"/>
+    <sheet name="11270" sheetId="75" r:id="rId75"/>
+    <sheet name="11493" sheetId="76" r:id="rId76"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="20">
   <si>
     <t>Ranks</t>
   </si>
@@ -70,10 +142,13 @@
     <t>Person</t>
   </si>
   <si>
-    <t>Tank</t>
+    <t>Swerve</t>
   </si>
   <si>
-    <t>Swerve</t>
+    <t>With neo</t>
+  </si>
+  <si>
+    <t>Tank</t>
   </si>
 </sst>
 </file>
@@ -412,6 +487,866 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
@@ -421,6 +1356,861 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H39"/>
@@ -507,6 +2297,866 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H39"/>
@@ -571,6 +3221,2667 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -591,4 +5902,950 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>